--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488271_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488271_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1541</v>
+        <v>12.7663</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9368</v>
+        <v>10.5243</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2173</v>
+        <v>2.242</v>
       </c>
       <c r="G2" t="n">
         <v>9.7363</v>
@@ -610,13 +610,13 @@
         <v>4.0763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4176</v>
+        <v>0.1946</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3656</v>
+        <v>0.222</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.052</v>
+        <v>-0.0274</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3144</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. TRUJILLO SUAREZ</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5754</v>
+        <v>6.3017</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3653</v>
+        <v>4.6695</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2101</v>
+        <v>1.6322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6288</v>
+        <v>5.435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9667</v>
+        <v>3.32</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3379</v>
+        <v>2.115</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3475</v>
+        <v>5.5151</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2017</v>
+        <v>3.2851</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1458</v>
+        <v>2.23</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7187</v>
+        <v>-0.0801</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.235</v>
+        <v>0.0349</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4837</v>
+        <v>-0.115</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1117</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9646</v>
+        <v>2.594</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0578</v>
+        <v>0.4051</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.3429</v>
       </c>
       <c r="U3" t="n">
-        <v>0.278</v>
+        <v>0.0621</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7771</v>
+        <v>1.5733</v>
       </c>
       <c r="W3" t="n">
-        <v>4.091</v>
+        <v>2.5172</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3139</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>S. TRUJILLO SUAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.812</v>
+        <v>6.2324</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1798</v>
+        <v>4.0716</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6322</v>
+        <v>2.1608</v>
       </c>
       <c r="G4" t="n">
-        <v>5.435</v>
+        <v>0.6288</v>
       </c>
       <c r="H4" t="n">
-        <v>3.32</v>
+        <v>0.9667</v>
       </c>
       <c r="I4" t="n">
-        <v>2.115</v>
+        <v>-0.3379</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5151</v>
+        <v>1.3475</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2851</v>
+        <v>1.2017</v>
       </c>
       <c r="L4" t="n">
-        <v>2.23</v>
+        <v>0.1458</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0801</v>
+        <v>-0.7187</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0349</v>
+        <v>-0.235</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.115</v>
+        <v>-0.4837</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1117</v>
+        <v>1.1117</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R4" t="n">
-        <v>2.594</v>
+        <v>2.9646</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0.7147</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1467</v>
+        <v>0.4859</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0621</v>
+        <v>0.2288</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5733</v>
+        <v>3.7771</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5172</v>
+        <v>4.091</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9439</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1669</v>
+        <v>4.2369</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9943</v>
+        <v>2.015</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1726</v>
+        <v>2.2219</v>
       </c>
       <c r="G5" t="n">
         <v>0.8683999999999999</v>
@@ -844,13 +844,13 @@
         <v>3.5205</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3721</v>
+        <v>0.4421</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8119</v>
+        <v>0.8326</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4397</v>
+        <v>-0.3905</v>
       </c>
       <c r="V5" t="n">
         <v>1.2589</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8126</v>
+        <v>2.0532</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2223</v>
+        <v>2.5368</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4097</v>
+        <v>-0.4835</v>
       </c>
       <c r="G6" t="n">
         <v>2.3593</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>0.953</v>
+        <v>0.1937</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9774</v>
+        <v>0.2919</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0244</v>
+        <v>-0.0982</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3144</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>A. BOTELLO GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3392</v>
+        <v>0.3262</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8051</v>
+        <v>0.1409</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4659</v>
+        <v>0.1853</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0248</v>
+        <v>0.0429</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0917</v>
+        <v>0.0429</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1165</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4428</v>
+        <v>0.0429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4509</v>
+        <v>0.0429</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9919</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.418</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5426</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8754</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3151</v>
+        <v>0.0979</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2151</v>
+        <v>0.0979</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5303</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BOTELLO GARCIA</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2282</v>
+        <v>0.2899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0429</v>
+        <v>2.8051</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1853</v>
+        <v>-2.5152</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0429</v>
+        <v>3.0248</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0429</v>
+        <v>-0.0917</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3.1165</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0429</v>
+        <v>4.4428</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0429</v>
+        <v>0.4509</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.9919</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.418</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.5426</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.8754</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.3644</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2151</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.5795</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3106</v>
+        <v>0.2529</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0555</v>
+        <v>0.4341</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2551</v>
+        <v>-0.1813</v>
       </c>
       <c r="G9" t="n">
         <v>0.9748</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1383</v>
+        <v>-0.5748</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5471</v>
+        <v>-0.0575</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.5173</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2589</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9969</v>
+        <v>-1.6785</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7688</v>
+        <v>-4.475</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7719</v>
+        <v>2.7965</v>
       </c>
       <c r="G10" t="n">
         <v>0.7295</v>
@@ -1234,13 +1234,13 @@
         <v>3.5205</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0594</v>
+        <v>0.259</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0174</v>
+        <v>0.3112</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0769</v>
+        <v>-0.0522</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6289</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>30.7809</v>
+        <v>30.781</v>
       </c>
       <c r="E11" t="n">
-        <v>22.7222</v>
+        <v>22.7223</v>
       </c>
       <c r="F11" t="n">
-        <v>8.058700000000002</v>
+        <v>8.0587</v>
       </c>
       <c r="G11" t="n">
         <v>23.7998</v>
@@ -1285,7 +1285,7 @@
         <v>12.5563</v>
       </c>
       <c r="J11" t="n">
-        <v>26.88320000000001</v>
+        <v>26.8832</v>
       </c>
       <c r="K11" t="n">
         <v>13.6369</v>
@@ -1303,7 +1303,7 @@
         <v>-0.6898999999999998</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7793</v>
+        <v>2.779300000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-17.6022</v>
@@ -1315,13 +1315,13 @@
         <v>1.3679</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7421</v>
+        <v>2.742</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3744</v>
+        <v>-1.3742</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8338</v>
+        <v>2.833799999999999</v>
       </c>
       <c r="W11" t="n">
         <v>10.6992</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.4672</v>
+        <v>6.4426</v>
       </c>
       <c r="E12" t="n">
         <v>9.8589</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3916</v>
+        <v>-3.4162</v>
       </c>
       <c r="G12" t="n">
         <v>5.9643</v>
@@ -1390,13 +1390,13 @@
         <v>3.1499</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0806</v>
+        <v>0.056</v>
       </c>
       <c r="T12" t="n">
         <v>0.3084</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2278</v>
+        <v>-0.2525</v>
       </c>
       <c r="V12" t="n">
         <v>2.831</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0234</v>
+        <v>0.1238</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0645</v>
+        <v>0.1138</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1321</v>
@@ -1546,13 +1546,13 @@
         <v>0.1853</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0766</v>
+        <v>0.0706</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.857</v>
+        <v>-2.2905</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5858</v>
+        <v>-0.9776</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2712</v>
+        <v>-1.3129</v>
       </c>
       <c r="G16" t="n">
         <v>-1.9968</v>
@@ -1702,13 +1702,13 @@
         <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3987</v>
+        <v>-0.0348</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4887</v>
+        <v>0.097</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09</v>
+        <v>-0.1318</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6294</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2131</v>
+        <v>-3.0613</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1935</v>
+        <v>-0.8838</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4066</v>
+        <v>-2.1775</v>
       </c>
       <c r="G17" t="n">
         <v>-4.3283</v>
@@ -1780,13 +1780,13 @@
         <v>3.1499</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0978</v>
+        <v>0.2496</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0519</v>
+        <v>0.9746</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.725</v>
       </c>
       <c r="V17" t="n">
         <v>1.5733</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7429</v>
+        <v>-3.1462</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2206</v>
+        <v>-2.9268</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5224</v>
+        <v>-0.2194</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2514</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.824</v>
+        <v>-0.2273</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2768</v>
+        <v>0.0261</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.1582</v>
+        <v>-4.2802</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1665</v>
+        <v>-2.3624</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9917</v>
+        <v>-1.9178</v>
       </c>
       <c r="G19" t="n">
         <v>-5.1246</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6138</v>
+        <v>0.4918</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.605</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.187</v>
+        <v>-0.1132</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9444</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.507</v>
+        <v>-4.8998</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7311</v>
+        <v>-1.927</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7759</v>
+        <v>-2.9728</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7251</v>
@@ -2014,13 +2014,13 @@
         <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0328</v>
+        <v>-0.36</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0037</v>
+        <v>-0.1996</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0365</v>
+        <v>-0.1604</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8946</v>
+        <v>-5.4525</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9028</v>
+        <v>-1.7113</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9918</v>
+        <v>-3.7412</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.4261</v>
+        <v>-3.2488</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1866</v>
+        <v>-2.3885</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.2395</v>
+        <v>-0.8602</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.581</v>
+        <v>1.8378</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.524</v>
+        <v>-0.0819</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.0569</v>
+        <v>1.9196</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8451</v>
+        <v>-5.0865</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6626</v>
+        <v>-2.3067</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1826</v>
+        <v>-2.7798</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>3.1499</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0244</v>
+        <v>-0.0746</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3954</v>
+        <v>0.1567</v>
       </c>
       <c r="U21" t="n">
-        <v>0.371</v>
+        <v>-0.2313</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0487</v>
+        <v>-5.823</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.103</v>
+        <v>-4.5111</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9457</v>
+        <v>-1.3118</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2488</v>
+        <v>-6.4261</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3885</v>
+        <v>-2.1866</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8602</v>
+        <v>-4.2395</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8378</v>
+        <v>-3.581</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0819</v>
+        <v>-0.524</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9196</v>
+        <v>-3.0569</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.0865</v>
+        <v>-2.8451</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3067</v>
+        <v>-1.6626</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7798</v>
+        <v>-1.1826</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1499</v>
+        <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6708</v>
+        <v>0.0473</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.235</v>
+        <v>-0.0037</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4358</v>
+        <v>0.051</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.5106</v>
+        <v>-7.4483</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5805</v>
+        <v>-2.895</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.9301</v>
+        <v>-4.5533</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4237</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8106</v>
+        <v>-0.7483</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9302</v>
+        <v>-0.2446</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8804</v>
+        <v>-0.5036</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8321</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-30.7809</v>
+        <v>-30.128</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.058499999999999</v>
+        <v>-8.0587</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.7225</v>
+        <v>-22.0691</v>
       </c>
       <c r="G24" t="n">
         <v>-23.7999</v>
@@ -2299,13 +2299,13 @@
         <v>-12.5563</v>
       </c>
       <c r="J24" t="n">
-        <v>3.083300000000001</v>
+        <v>3.083300000000002</v>
       </c>
       <c r="K24" t="n">
         <v>2.3934</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6898999999999994</v>
+        <v>0.6898999999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-26.8833</v>
@@ -2326,13 +2326,13 @@
         <v>17.6023</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.368</v>
+        <v>-0.715</v>
       </c>
       <c r="T24" t="n">
-        <v>1.3744</v>
+        <v>1.3742</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.7422</v>
+        <v>-2.0892</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8338</v>
